--- a/CPP_Grades_Final.xlsx
+++ b/CPP_Grades_Final.xlsx
@@ -1170,8 +1170,12 @@
       <c r="F23" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="G23" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>70.2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">

--- a/CPP_Grades_Final.xlsx
+++ b/CPP_Grades_Final.xlsx
@@ -1260,8 +1260,12 @@
       <c r="F26" s="2" t="n">
         <v>84.5</v>
       </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="G26" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>77.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1582,8 +1586,12 @@
       <c r="F37" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="G37" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>85.90000000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1756,7 +1764,9 @@
       <c r="F43" s="4" t="n">
         <v>78.5</v>
       </c>
-      <c r="G43" s="4" t="n"/>
+      <c r="G43" s="4" t="n">
+        <v>73</v>
+      </c>
       <c r="H43" s="4" t="n"/>
     </row>
     <row r="44">

--- a/CPP_Grades_Final.xlsx
+++ b/CPP_Grades_Final.xlsx
@@ -1530,8 +1530,12 @@
       <c r="F35" s="4" t="n">
         <v>84.5</v>
       </c>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
+      <c r="G35" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>82.84999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">

--- a/CPP_Grades_Final.xlsx
+++ b/CPP_Grades_Final.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +27,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -43,26 +47,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
+        <fgColor rgb="FF2E4057"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4F8"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B998B"/>
+        <fgColor rgb="FFF7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FF1A936F"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,55 +74,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -489,13 +464,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -545,36 +520,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr"/>
-      <c r="C2" s="7" t="inlineStr"/>
-      <c r="D2" s="8">
-        <f>AVERAGE(D3:D103)</f>
-        <v/>
-      </c>
-      <c r="E2" s="8">
-        <f>AVERAGE(E3:E103)</f>
-        <v/>
-      </c>
-      <c r="F2" s="8">
-        <f>AVERAGE(F3:F103)</f>
-        <v/>
-      </c>
-      <c r="G2" s="8">
-        <f>AVERAGE(G3:G103)</f>
-        <v/>
-      </c>
-      <c r="H2" s="8">
-        <f>AVERAGE(H3:H103)</f>
-        <v/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>85.09</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2023905492</t>
         </is>
@@ -589,20 +559,20 @@
           <t>Doris (陈怡彤)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>64</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>68</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="4">
@@ -611,12 +581,12 @@
           <t>2023905494</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>陈亦力</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Vernon</t>
         </is>
@@ -634,11 +604,11 @@
         <v>67</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2023905495</t>
         </is>
@@ -653,16 +623,16 @@
           <t>Verena</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>92.5</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -675,12 +645,12 @@
           <t>2024900591</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>杨思远</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
@@ -702,7 +672,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2024900592</t>
         </is>
@@ -717,16 +687,16 @@
           <t>Winham</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>92</v>
       </c>
       <c r="H7" s="4" t="n">
@@ -739,12 +709,12 @@
           <t>2024900593</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>李静雯</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Livia</t>
         </is>
@@ -766,7 +736,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2024900594</t>
         </is>
@@ -781,16 +751,16 @@
           <t>Daniel</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H9" s="4" t="n">
@@ -803,12 +773,12 @@
           <t>2024900595</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>尤天豪</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Johnny</t>
         </is>
@@ -830,7 +800,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2024900596</t>
         </is>
@@ -845,16 +815,16 @@
           <t>Ivan</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>95</v>
       </c>
       <c r="H11" s="4" t="n">
@@ -867,12 +837,12 @@
           <t>2024900597</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>洪浩洋</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Buck</t>
         </is>
@@ -894,7 +864,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2024900794</t>
         </is>
@@ -909,16 +879,16 @@
           <t>Freya</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H13" s="4" t="n">
@@ -931,12 +901,12 @@
           <t>2024900795</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>孙希彤</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Echo</t>
         </is>
@@ -958,7 +928,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2024900796</t>
         </is>
@@ -973,16 +943,16 @@
           <t>Nancy (张慧珍)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H15" s="4" t="n">
@@ -995,12 +965,12 @@
           <t>2024900797</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>周子童</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Maple</t>
         </is>
@@ -1022,7 +992,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2024900798</t>
         </is>
@@ -1037,16 +1007,16 @@
           <t>Pojock</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H17" s="4" t="n">
@@ -1059,12 +1029,12 @@
           <t>2024900799</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>杨振宇</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Riley</t>
         </is>
@@ -1086,7 +1056,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2024900800</t>
         </is>
@@ -1101,16 +1071,16 @@
           <t>Peter</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>87.5</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>91</v>
       </c>
       <c r="H19" s="4" t="n">
@@ -1123,12 +1093,12 @@
           <t>2024900801</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>温箬瑄</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Alysa</t>
         </is>
@@ -1150,7 +1120,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2024900802</t>
         </is>
@@ -1165,16 +1135,16 @@
           <t>Valentine</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>95</v>
       </c>
       <c r="H21" s="4" t="n">
@@ -1187,12 +1157,12 @@
           <t>2024900803</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>王朝新</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Zack</t>
         </is>
@@ -1214,7 +1184,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>2024900804</t>
         </is>
@@ -1229,16 +1199,16 @@
           <t>Melkiades</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H23" s="4" t="n">
@@ -1251,12 +1221,12 @@
           <t>2024900805</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>陈宣睿</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
@@ -1278,7 +1248,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>2024900806</t>
         </is>
@@ -1293,16 +1263,16 @@
           <t>Eric (Hu Weilin)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H25" s="4" t="n">
@@ -1315,12 +1285,12 @@
           <t>2024900807</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>刘奕博</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Eason (刘奕博)</t>
         </is>
@@ -1342,7 +1312,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>2024900808</t>
         </is>
@@ -1357,16 +1327,16 @@
           <t>Jimmy</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>84.5</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>88</v>
       </c>
       <c r="H27" s="4" t="n">
@@ -1379,12 +1349,12 @@
           <t>2024900809</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>马澍晗</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Carry</t>
         </is>
@@ -1406,7 +1376,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>2024900810</t>
         </is>
@@ -1421,16 +1391,16 @@
           <t>Makayla</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G29" s="3" t="n">
         <v>93</v>
       </c>
       <c r="H29" s="4" t="n">
@@ -1443,12 +1413,12 @@
           <t>2024900811</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>刘旭朗</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Aleksib</t>
         </is>
@@ -1470,7 +1440,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>2024900812</t>
         </is>
@@ -1485,16 +1455,16 @@
           <t>Keith (王樱棋)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G31" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H31" s="4" t="n">
@@ -1507,12 +1477,12 @@
           <t>2024900813</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>王田愈可</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Froncois</t>
         </is>
@@ -1534,7 +1504,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>2024900814</t>
         </is>
@@ -1549,16 +1519,16 @@
           <t>Gillian</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>94</v>
       </c>
       <c r="H33" s="4" t="n">
@@ -1571,12 +1541,12 @@
           <t>2024900815</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>路恒</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Henry</t>
         </is>
@@ -1598,7 +1568,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>2024902256</t>
         </is>
@@ -1613,16 +1583,16 @@
           <t>Latain</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G35" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H35" s="4" t="n">
@@ -1635,12 +1605,12 @@
           <t>2024902257</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>程星凯</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
@@ -1662,7 +1632,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>2024902258</t>
         </is>
@@ -1677,16 +1647,16 @@
           <t>Liesel</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G37" s="3" t="n">
         <v>71</v>
       </c>
       <c r="H37" s="4" t="n">
@@ -1699,12 +1669,12 @@
           <t>2024902259</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>魏磊磊</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Simon</t>
         </is>
@@ -1726,7 +1696,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>2024902260</t>
         </is>
@@ -1741,16 +1711,16 @@
           <t>Tom</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H39" s="4" t="n">
@@ -1763,12 +1733,12 @@
           <t>2024902261</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>吕伟涛</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Smody (吕伟涛)</t>
         </is>
@@ -1790,7 +1760,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>2024902262</t>
         </is>
@@ -1805,16 +1775,16 @@
           <t>Kenley</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>91</v>
       </c>
       <c r="H41" s="4" t="n">
@@ -1827,12 +1797,12 @@
           <t>2024902263</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>吴丰年</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Emile</t>
         </is>
@@ -1854,7 +1824,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>2024902264</t>
         </is>
@@ -1869,16 +1839,16 @@
           <t>Brown</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>84</v>
       </c>
       <c r="H43" s="4" t="n">
@@ -1891,12 +1861,12 @@
           <t>2024902265</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>冯天宇</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Arrco</t>
         </is>
@@ -1914,7 +1884,7 @@
       <c r="H44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>2024902583</t>
         </is>
@@ -1929,16 +1899,16 @@
           <t>Jesko (张效通)</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H45" s="4" t="n">
@@ -1951,12 +1921,12 @@
           <t>2024902584</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>伍宇轩</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Othersen</t>
         </is>
@@ -1978,7 +1948,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>2024902585</t>
         </is>
@@ -1993,16 +1963,16 @@
           <t>Simon</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>84</v>
       </c>
       <c r="H47" s="4" t="n">
@@ -2015,12 +1985,12 @@
           <t>2024902586</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>张馨艺</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Betty</t>
         </is>
@@ -2042,7 +2012,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>2024902587</t>
         </is>
@@ -2057,16 +2027,16 @@
           <t>Shane</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="3" t="n">
         <v>89.5</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H49" s="4" t="n">
@@ -2079,12 +2049,12 @@
           <t>2024902588</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>陈卫政</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Judge</t>
         </is>
@@ -2106,7 +2076,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>2024902589</t>
         </is>
@@ -2121,16 +2091,16 @@
           <t>Robin</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H51" s="4" t="n">
@@ -2143,12 +2113,12 @@
           <t>2024902590</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>彭程</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Leo</t>
         </is>
@@ -2170,7 +2140,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>2024902591</t>
         </is>
@@ -2185,16 +2155,16 @@
           <t>Arthur</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G53" s="3" t="n">
         <v>84</v>
       </c>
       <c r="H53" s="4" t="n">
@@ -2207,12 +2177,12 @@
           <t>2024902592</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>陈昱杨</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Mike</t>
         </is>
@@ -2234,7 +2204,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>2024903032</t>
         </is>
@@ -2249,16 +2219,16 @@
           <t>Upster</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H55" s="4" t="n">
@@ -2271,12 +2241,12 @@
           <t>2024903033</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>何澎瑞</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Simple</t>
         </is>
@@ -2298,7 +2268,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>2024903034</t>
         </is>
@@ -2313,16 +2283,16 @@
           <t>Daniel</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <v>95</v>
       </c>
       <c r="H57" s="4" t="n">
@@ -2335,12 +2305,12 @@
           <t>2024903035</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>曹润忱</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Clare</t>
         </is>
@@ -2362,7 +2332,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>2024903036</t>
         </is>
@@ -2377,16 +2347,16 @@
           <t>Alice (李培生)</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H59" s="4" t="n">
@@ -2399,12 +2369,12 @@
           <t>2024903381</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>张煜琳</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Borios</t>
         </is>
@@ -2426,7 +2396,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>2024903382</t>
         </is>
@@ -2441,16 +2411,16 @@
           <t>Yori</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="3" t="n">
         <v>87</v>
       </c>
       <c r="H61" s="4" t="n">
@@ -2463,12 +2433,12 @@
           <t>2024903383</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>黄士涵</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Hilbert</t>
         </is>
@@ -2490,7 +2460,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>2024903384</t>
         </is>
@@ -2505,16 +2475,16 @@
           <t>Mika</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="3" t="n">
         <v>74</v>
       </c>
       <c r="H63" s="4" t="n">
@@ -2527,12 +2497,12 @@
           <t>2024903385</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>孙一凡</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Carl</t>
         </is>
@@ -2554,7 +2524,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>2024903386</t>
         </is>
@@ -2569,16 +2539,16 @@
           <t>Jelly</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H65" s="4" t="n">
@@ -2591,12 +2561,12 @@
           <t>2024903387</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>彭康</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Ronaldo</t>
         </is>
@@ -2618,7 +2588,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>2024903530</t>
         </is>
@@ -2633,16 +2603,16 @@
           <t>Ramos</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>88</v>
       </c>
       <c r="H67" s="4" t="n">
@@ -2655,12 +2625,12 @@
           <t>2024903531</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>何贵霖</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
@@ -2682,7 +2652,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>2024903532</t>
         </is>
@@ -2697,16 +2667,16 @@
           <t>Violet</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="3" t="n">
         <v>78.5</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G69" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H69" s="4" t="n">
@@ -2719,12 +2689,12 @@
           <t>2024903533</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>张中子墨</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Nimo</t>
         </is>
@@ -2746,7 +2716,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>2024903534</t>
         </is>
@@ -2761,16 +2731,16 @@
           <t>Noah</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F71" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G71" s="3" t="n">
         <v>92</v>
       </c>
       <c r="H71" s="4" t="n">
@@ -2783,12 +2753,12 @@
           <t>2024903709</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>项阳洋</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Deckard (项阳洋)</t>
         </is>
@@ -2810,7 +2780,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>2024903710</t>
         </is>
@@ -2825,16 +2795,16 @@
           <t>Sky</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="3" t="n">
         <v>87.5</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G73" s="3" t="n">
         <v>75</v>
       </c>
       <c r="H73" s="4" t="n">
@@ -2847,12 +2817,12 @@
           <t>2024903711</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>黄玮博</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Rafael (Huang Weibo)</t>
         </is>
@@ -2874,7 +2844,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>2024903712</t>
         </is>
@@ -2889,16 +2859,16 @@
           <t>Andy</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="3" t="n">
         <v>90.5</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G75" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H75" s="4" t="n">
@@ -2911,12 +2881,12 @@
           <t>2024903713</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>王澄</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
@@ -2938,7 +2908,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>2024903715</t>
         </is>
@@ -2953,16 +2923,16 @@
           <t>Simon Nian</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G77" s="3" t="n">
         <v>98</v>
       </c>
       <c r="H77" s="4" t="n">
@@ -2975,12 +2945,12 @@
           <t>2024903716</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>俞思源</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Carter</t>
         </is>
@@ -3002,7 +2972,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>2024903717</t>
         </is>
@@ -3017,16 +2987,16 @@
           <t>Charles (Lu Yucheng)</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G79" s="3" t="n">
         <v>94</v>
       </c>
       <c r="H79" s="4" t="n">
@@ -3039,12 +3009,12 @@
           <t>2024903718</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>应铭豪</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Sisyphus</t>
         </is>
@@ -3066,7 +3036,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>2024904082</t>
         </is>
@@ -3081,16 +3051,16 @@
           <t>Tohsaka</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="G81" s="2" t="n"/>
+      <c r="G81" s="3" t="n"/>
       <c r="H81" s="4" t="n"/>
     </row>
     <row r="82">
@@ -3099,12 +3069,12 @@
           <t>2024904083</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>刘子墨</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Laura (刘子墨)</t>
         </is>
@@ -3126,7 +3096,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>2024904084</t>
         </is>
@@ -3141,16 +3111,16 @@
           <t>Alex</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D83" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E83" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G83" s="3" t="n">
         <v>81</v>
       </c>
       <c r="H83" s="4" t="n">
@@ -3163,12 +3133,12 @@
           <t>2024904085</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>谢明锦</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>Lucy</t>
         </is>
@@ -3190,7 +3160,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>2024904086</t>
         </is>
@@ -3205,16 +3175,16 @@
           <t>Melody</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="3" t="n">
         <v>86.5</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G85" s="3" t="n">
         <v>88</v>
       </c>
       <c r="H85" s="4" t="n">
@@ -3227,12 +3197,12 @@
           <t>2024904087</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>李雪健</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Leeking</t>
         </is>
@@ -3254,7 +3224,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>2024904088</t>
         </is>
@@ -3269,16 +3239,16 @@
           <t>Han (王子涵)</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D87" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G87" s="3" t="n">
         <v>77</v>
       </c>
       <c r="H87" s="4" t="n">
@@ -3291,12 +3261,12 @@
           <t>2024904089</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>王帅然</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>Jasonbond (王帅然)</t>
         </is>
@@ -3318,7 +3288,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>2024904090</t>
         </is>
@@ -3333,16 +3303,16 @@
           <t>Rhys (肖梓涵)</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E89" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F89" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="G89" s="3" t="n">
         <v>93</v>
       </c>
       <c r="H89" s="4" t="n">
@@ -3355,12 +3325,12 @@
           <t>2024904717</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>李宇飞</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Ricardo</t>
         </is>
@@ -3382,7 +3352,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>2024904718</t>
         </is>
@@ -3397,16 +3367,16 @@
           <t>Johnson</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="G91" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H91" s="4" t="n">
@@ -3419,12 +3389,12 @@
           <t>2024904719</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>李思远</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Sakuya (李思远)</t>
         </is>
@@ -3446,7 +3416,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>2024904720</t>
         </is>
@@ -3461,16 +3431,16 @@
           <t>Ike</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F93" s="3" t="n">
         <v>90.5</v>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="G93" s="3" t="n">
         <v>67</v>
       </c>
       <c r="H93" s="4" t="n">
@@ -3483,12 +3453,12 @@
           <t>2024904721</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>王泽翰</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Brimstone</t>
         </is>
@@ -3510,7 +3480,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>2024904787</t>
         </is>
@@ -3525,16 +3495,16 @@
           <t>Victoria (郭星彤)</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D95" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F95" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="G95" s="2" t="n">
+      <c r="G95" s="3" t="n">
         <v>92</v>
       </c>
       <c r="H95" s="4" t="n">
@@ -3547,12 +3517,12 @@
           <t>2024904788</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>杨德洲</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>Tiara</t>
         </is>
@@ -3574,7 +3544,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>2024904789</t>
         </is>
@@ -3589,16 +3559,16 @@
           <t>Jett (唐健乔)</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D97" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="F97" s="2" t="n">
+      <c r="F97" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="G97" s="2" t="n">
+      <c r="G97" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H97" s="4" t="n">
@@ -3611,12 +3581,12 @@
           <t>2024904790</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>王恩奇</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Akali (王恩奇)</t>
         </is>
@@ -3638,7 +3608,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>2024904791</t>
         </is>
@@ -3653,16 +3623,16 @@
           <t>Stella</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D99" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="G99" s="2" t="n">
+      <c r="G99" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H99" s="4" t="n">
@@ -3675,12 +3645,12 @@
           <t>2024905118</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>程文烨</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Cooper</t>
         </is>
@@ -3702,7 +3672,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>2024905120</t>
         </is>
@@ -3717,16 +3687,16 @@
           <t>Serein</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D101" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="E101" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F101" s="2" t="n">
+      <c r="F101" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="G101" s="2" t="n">
+      <c r="G101" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H101" s="4" t="n">
@@ -3739,12 +3709,12 @@
           <t>2024905121</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>吴昊宸</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Stephen</t>
         </is>
@@ -3766,7 +3736,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>2024905122</t>
         </is>
@@ -3781,16 +3751,16 @@
           <t>Log</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D103" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="F103" s="2" t="n">
+      <c r="F103" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="G103" s="2" t="n">
+      <c r="G103" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H103" s="4" t="n">

--- a/CPP_Grades_Final.xlsx
+++ b/CPP_Grades_Final.xlsx
@@ -528,7 +528,7 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n">
-        <v>61.84</v>
+        <v>62.02</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>86.06999999999999</v>
@@ -537,10 +537,10 @@
         <v>88.33</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>87.44</v>
+        <v>86.52</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>85.09</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="3">
@@ -1871,7 +1871,9 @@
           <t>Arrco</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
+      <c r="D44" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="E44" s="5" t="n">
         <v>48</v>
       </c>
@@ -1879,9 +1881,11 @@
         <v>78.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="H44" s="4" t="n"/>
+        <v>68</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>68.34999999999999</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -3060,8 +3064,12 @@
       <c r="F81" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">

--- a/CPP_Grades_Final.xlsx
+++ b/CPP_Grades_Final.xlsx
@@ -3065,10 +3065,10 @@
         <v>83</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>45</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="82">
